--- a/hall/resources/sample/UpcomingMobileGame.xlsx
+++ b/hall/resources/sample/UpcomingMobileGame.xlsx
@@ -404,7 +404,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -415,12 +415,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -569,12 +563,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -915,137 +909,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1053,9 +1047,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1448,8 +1439,8 @@
       <c r="E5" s="1">
         <v>44002</v>
       </c>
-      <c r="F5" s="3" t="b">
-        <v>0</v>
+      <c r="F5" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1468,8 +1459,8 @@
       <c r="E6" s="1">
         <v>44003</v>
       </c>
-      <c r="F6" s="3" t="b">
-        <v>0</v>
+      <c r="F6" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1488,8 +1479,8 @@
       <c r="E7" s="1">
         <v>44004</v>
       </c>
-      <c r="F7" s="3" t="b">
-        <v>0</v>
+      <c r="F7" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1508,8 +1499,8 @@
       <c r="E8" s="1">
         <v>44005</v>
       </c>
-      <c r="F8" s="3" t="b">
-        <v>0</v>
+      <c r="F8" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1548,8 +1539,8 @@
       <c r="E10" s="1">
         <v>44007</v>
       </c>
-      <c r="F10" s="3" t="b">
-        <v>0</v>
+      <c r="F10" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1568,8 +1559,8 @@
       <c r="E11" s="1">
         <v>44008</v>
       </c>
-      <c r="F11" s="3" t="b">
-        <v>0</v>
+      <c r="F11" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1588,8 +1579,8 @@
       <c r="E12" s="1">
         <v>44009</v>
       </c>
-      <c r="F12" s="3" t="b">
-        <v>0</v>
+      <c r="F12" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1608,8 +1599,8 @@
       <c r="E13" s="1">
         <v>44010</v>
       </c>
-      <c r="F13" s="3" t="b">
-        <v>0</v>
+      <c r="F13" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1628,8 +1619,8 @@
       <c r="E14" s="1">
         <v>44011</v>
       </c>
-      <c r="F14" s="3" t="b">
-        <v>0</v>
+      <c r="F14" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1648,8 +1639,8 @@
       <c r="E15" s="1">
         <v>44012</v>
       </c>
-      <c r="F15" s="3" t="b">
-        <v>0</v>
+      <c r="F15" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1668,8 +1659,8 @@
       <c r="E16" s="1">
         <v>44013</v>
       </c>
-      <c r="F16" s="3" t="b">
-        <v>0</v>
+      <c r="F16" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1748,8 +1739,8 @@
       <c r="E20" s="1">
         <v>44017</v>
       </c>
-      <c r="F20" s="3" t="b">
-        <v>0</v>
+      <c r="F20" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1868,8 +1859,8 @@
       <c r="E26" s="1">
         <v>44023</v>
       </c>
-      <c r="F26" s="3" t="b">
-        <v>0</v>
+      <c r="F26" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -2288,8 +2279,8 @@
       <c r="E47" s="1">
         <v>44044</v>
       </c>
-      <c r="F47" s="3" t="b">
-        <v>0</v>
+      <c r="F47" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:6">

--- a/hall/resources/sample/UpcomingMobileGame.xlsx
+++ b/hall/resources/sample/UpcomingMobileGame.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\common\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4021EA42-2485-4CF8-B497-31A6CBED1652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UpcomingMobileGame" sheetId="1" r:id="rId1"/>
@@ -29,12 +35,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -62,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="122">
   <si>
     <t>游戏id</t>
   </si>
@@ -392,19 +398,49 @@
   </si>
   <si>
     <t>yxqdb_tu_49</t>
+  </si>
+  <si>
+    <t>yxqdb_tu_50</t>
+  </si>
+  <si>
+    <t>yxqdb_tu_51</t>
+  </si>
+  <si>
+    <t>yxqdb_tu_52</t>
+  </si>
+  <si>
+    <t>yxqdb_tu_53</t>
+  </si>
+  <si>
+    <t>yxqdb_tu_54</t>
+  </si>
+  <si>
+    <t>yxqdb_tu_55</t>
+  </si>
+  <si>
+    <t>英雄联盟</t>
+  </si>
+  <si>
+    <t>魔童降世</t>
+  </si>
+  <si>
+    <t>五龙争霸</t>
+  </si>
+  <si>
+    <t>航海王</t>
+  </si>
+  <si>
+    <t>精灵宝可梦</t>
+  </si>
+  <si>
+    <t>部落冲突</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -425,150 +461,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -579,202 +471,29 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -797,323 +516,80 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1363,14 +839,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F52"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F58"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="13.25" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.25" style="1" customWidth="1"/>
@@ -1378,7 +854,7 @@
     <col min="4" max="6" width="14.875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1398,7 +874,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -1415,7 +891,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -1432,7 +908,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1452,7 +928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -1472,7 +948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -1492,7 +968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -1512,7 +988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -1532,7 +1008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -1552,7 +1028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -1572,7 +1048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -1592,7 +1068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -1612,7 +1088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -1632,7 +1108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -1652,7 +1128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -1672,7 +1148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -1692,7 +1168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -1712,7 +1188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -1732,7 +1208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -1752,7 +1228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -1772,7 +1248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -1792,7 +1268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -1812,7 +1288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -1832,7 +1308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>21</v>
       </c>
@@ -1852,7 +1328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>22</v>
       </c>
@@ -1872,7 +1348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -1892,7 +1368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -1912,7 +1388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>25</v>
       </c>
@@ -1932,7 +1408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>26</v>
       </c>
@@ -1952,7 +1428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>27</v>
       </c>
@@ -1972,7 +1448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>28</v>
       </c>
@@ -1992,7 +1468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>29</v>
       </c>
@@ -2012,7 +1488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>30</v>
       </c>
@@ -2032,7 +1508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
         <v>31</v>
       </c>
@@ -2052,7 +1528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
         <v>32</v>
       </c>
@@ -2072,7 +1548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
         <v>33</v>
       </c>
@@ -2092,7 +1568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
         <v>34</v>
       </c>
@@ -2112,7 +1588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
         <v>35</v>
       </c>
@@ -2132,7 +1608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
         <v>36</v>
       </c>
@@ -2152,7 +1628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
         <v>37</v>
       </c>
@@ -2172,7 +1648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
         <v>38</v>
       </c>
@@ -2192,7 +1668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
         <v>39</v>
       </c>
@@ -2212,7 +1688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
         <v>40</v>
       </c>
@@ -2232,7 +1708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
         <v>41</v>
       </c>
@@ -2252,7 +1728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
         <v>42</v>
       </c>
@@ -2272,7 +1748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
         <v>43</v>
       </c>
@@ -2292,7 +1768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
         <v>44</v>
       </c>
@@ -2312,7 +1788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
         <v>45</v>
       </c>
@@ -2332,7 +1808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
         <v>46</v>
       </c>
@@ -2352,7 +1828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
         <v>47</v>
       </c>
@@ -2372,7 +1848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
         <v>48</v>
       </c>
@@ -2392,34 +1868,152 @@
         <v>1</v>
       </c>
     </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A53" s="1">
+        <v>49</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D53" s="1">
+        <v>44100</v>
+      </c>
+      <c r="E53" s="1">
+        <v>44106</v>
+      </c>
+      <c r="F53" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A54" s="1">
+        <v>50</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D54" s="1">
+        <v>44101</v>
+      </c>
+      <c r="E54" s="1">
+        <v>44107</v>
+      </c>
+      <c r="F54" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A55" s="1">
+        <v>51</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D55" s="1">
+        <v>44102</v>
+      </c>
+      <c r="E55" s="1">
+        <v>44108</v>
+      </c>
+      <c r="F55" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A56" s="1">
+        <v>52</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D56" s="1">
+        <v>44103</v>
+      </c>
+      <c r="E56" s="1">
+        <v>44109</v>
+      </c>
+      <c r="F56" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A57" s="1">
+        <v>53</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D57" s="1">
+        <v>44105</v>
+      </c>
+      <c r="E57" s="1">
+        <v>44111</v>
+      </c>
+      <c r="F57" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A58" s="1">
+        <v>54</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D58" s="1">
+        <v>44104</v>
+      </c>
+      <c r="E58" s="1">
+        <v>44110</v>
+      </c>
+      <c r="F58" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/hall/resources/sample/UpcomingMobileGame.xlsx
+++ b/hall/resources/sample/UpcomingMobileGame.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\common\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4021EA42-2485-4CF8-B497-31A6CBED1652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UpcomingMobileGame" sheetId="1" r:id="rId1"/>
@@ -29,12 +35,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -62,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="122">
   <si>
     <t>游戏id</t>
   </si>
@@ -392,19 +398,49 @@
   </si>
   <si>
     <t>yxqdb_tu_49</t>
+  </si>
+  <si>
+    <t>yxqdb_tu_50</t>
+  </si>
+  <si>
+    <t>yxqdb_tu_51</t>
+  </si>
+  <si>
+    <t>yxqdb_tu_52</t>
+  </si>
+  <si>
+    <t>yxqdb_tu_53</t>
+  </si>
+  <si>
+    <t>yxqdb_tu_54</t>
+  </si>
+  <si>
+    <t>yxqdb_tu_55</t>
+  </si>
+  <si>
+    <t>英雄联盟</t>
+  </si>
+  <si>
+    <t>魔童降世</t>
+  </si>
+  <si>
+    <t>五龙争霸</t>
+  </si>
+  <si>
+    <t>航海王</t>
+  </si>
+  <si>
+    <t>精灵宝可梦</t>
+  </si>
+  <si>
+    <t>部落冲突</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -419,152 +455,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -573,202 +466,34 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -791,320 +516,80 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+  </cellStyleXfs>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-  </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1354,14 +839,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F52"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F58"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="13.25" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.25" style="1" customWidth="1"/>
@@ -1369,7 +854,7 @@
     <col min="4" max="6" width="14.875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1389,7 +874,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -1406,7 +891,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -1423,7 +908,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1439,11 +924,11 @@
       <c r="E5" s="1">
         <v>44002</v>
       </c>
-      <c r="F5" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="F5" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -1459,11 +944,11 @@
       <c r="E6" s="1">
         <v>44003</v>
       </c>
-      <c r="F6" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="F6" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -1479,11 +964,11 @@
       <c r="E7" s="1">
         <v>44004</v>
       </c>
-      <c r="F7" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="F7" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -1499,11 +984,11 @@
       <c r="E8" s="1">
         <v>44005</v>
       </c>
-      <c r="F8" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="F8" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -1523,7 +1008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -1539,11 +1024,11 @@
       <c r="E10" s="1">
         <v>44007</v>
       </c>
-      <c r="F10" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="F10" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -1559,11 +1044,11 @@
       <c r="E11" s="1">
         <v>44008</v>
       </c>
-      <c r="F11" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="F11" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -1579,11 +1064,11 @@
       <c r="E12" s="1">
         <v>44009</v>
       </c>
-      <c r="F12" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="F12" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -1599,11 +1084,11 @@
       <c r="E13" s="1">
         <v>44010</v>
       </c>
-      <c r="F13" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="F13" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -1619,11 +1104,11 @@
       <c r="E14" s="1">
         <v>44011</v>
       </c>
-      <c r="F14" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="F14" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -1639,11 +1124,11 @@
       <c r="E15" s="1">
         <v>44012</v>
       </c>
-      <c r="F15" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="F15" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -1659,11 +1144,11 @@
       <c r="E16" s="1">
         <v>44013</v>
       </c>
-      <c r="F16" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="F16" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -1683,7 +1168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -1703,7 +1188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -1723,7 +1208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>16</v>
       </c>
@@ -1739,11 +1224,11 @@
       <c r="E20" s="1">
         <v>44017</v>
       </c>
-      <c r="F20" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="F20" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>17</v>
       </c>
@@ -1763,7 +1248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>18</v>
       </c>
@@ -1783,7 +1268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -1803,7 +1288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>20</v>
       </c>
@@ -1823,7 +1308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>21</v>
       </c>
@@ -1843,7 +1328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>22</v>
       </c>
@@ -1859,11 +1344,11 @@
       <c r="E26" s="1">
         <v>44023</v>
       </c>
-      <c r="F26" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+      <c r="F26" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -1883,7 +1368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -1903,7 +1388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>25</v>
       </c>
@@ -1923,7 +1408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>26</v>
       </c>
@@ -1943,7 +1428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>27</v>
       </c>
@@ -1963,7 +1448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>28</v>
       </c>
@@ -1983,7 +1468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>29</v>
       </c>
@@ -2003,7 +1488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>30</v>
       </c>
@@ -2023,7 +1508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
         <v>31</v>
       </c>
@@ -2043,7 +1528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
         <v>32</v>
       </c>
@@ -2063,7 +1548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
         <v>33</v>
       </c>
@@ -2083,7 +1568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
         <v>34</v>
       </c>
@@ -2103,7 +1588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
         <v>35</v>
       </c>
@@ -2123,7 +1608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
         <v>36</v>
       </c>
@@ -2143,7 +1628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
         <v>37</v>
       </c>
@@ -2163,7 +1648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
         <v>38</v>
       </c>
@@ -2183,7 +1668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
         <v>39</v>
       </c>
@@ -2203,7 +1688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
         <v>40</v>
       </c>
@@ -2223,7 +1708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
         <v>41</v>
       </c>
@@ -2243,7 +1728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
         <v>42</v>
       </c>
@@ -2263,7 +1748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
         <v>43</v>
       </c>
@@ -2279,11 +1764,11 @@
       <c r="E47" s="1">
         <v>44044</v>
       </c>
-      <c r="F47" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="F47" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
         <v>44</v>
       </c>
@@ -2303,7 +1788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
         <v>45</v>
       </c>
@@ -2323,7 +1808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
         <v>46</v>
       </c>
@@ -2343,7 +1828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
         <v>47</v>
       </c>
@@ -2363,7 +1848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
         <v>48</v>
       </c>
@@ -2383,34 +1868,152 @@
         <v>1</v>
       </c>
     </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A53" s="1">
+        <v>49</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D53" s="1">
+        <v>44100</v>
+      </c>
+      <c r="E53" s="1">
+        <v>44106</v>
+      </c>
+      <c r="F53" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A54" s="1">
+        <v>50</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D54" s="1">
+        <v>44101</v>
+      </c>
+      <c r="E54" s="1">
+        <v>44107</v>
+      </c>
+      <c r="F54" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A55" s="1">
+        <v>51</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D55" s="1">
+        <v>44102</v>
+      </c>
+      <c r="E55" s="1">
+        <v>44108</v>
+      </c>
+      <c r="F55" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A56" s="1">
+        <v>52</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D56" s="1">
+        <v>44103</v>
+      </c>
+      <c r="E56" s="1">
+        <v>44109</v>
+      </c>
+      <c r="F56" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A57" s="1">
+        <v>53</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D57" s="1">
+        <v>44105</v>
+      </c>
+      <c r="E57" s="1">
+        <v>44111</v>
+      </c>
+      <c r="F57" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A58" s="1">
+        <v>54</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D58" s="1">
+        <v>44104</v>
+      </c>
+      <c r="E58" s="1">
+        <v>44110</v>
+      </c>
+      <c r="F58" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>